--- a/output/pdf_financials_xlsx/BEA.xlsx
+++ b/output/pdf_financials_xlsx/BEA.xlsx
@@ -1373,7 +1373,7 @@
         <v>0.337789</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.988729</v>
+        <v>-0.988729</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.501323</v>
@@ -1435,7 +1435,7 @@
         <v>0.00346</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.675578</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.27746</v>
+        <v>-0.27746</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.806543</v>
+        <v>-0.806543</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.629999</v>
+        <v>-0.629999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.337789</v>
+        <v>-0.337789</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.988729</v>
+        <v>-0.988729</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.501323</v>
@@ -1880,19 +1880,19 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.27746</v>
+        <v>-0.27746</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.806543</v>
+        <v>-0.806543</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.629999</v>
+        <v>-0.629999</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.337789</v>
+        <v>-0.337789</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.988729</v>
+        <v>-0.988729</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.501323</v>
@@ -2075,19 +2075,19 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>4.624333</v>
+        <v>-4.624333</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-5.376953</v>
+        <v>5.376953</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-12.59998</v>
+        <v>12.59998</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-16.88945</v>
+        <v>16.88945</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-14.1247</v>
+        <v>14.1247</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>16.710767</v>
@@ -2164,7 +2164,7 @@
         <v>0.337789</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.988729</v>
+        <v>-0.988729</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.501323</v>
@@ -2294,7 +2294,7 @@
         <v>0.337789</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.988729</v>
+        <v>-0.988729</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.501323</v>
@@ -2453,10 +2453,10 @@
         <v>0.5462074104243526</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -6244,55 +6244,55 @@
         <v>0.320971</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.391072</v>
+        <v>0.624163</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.412419</v>
+        <v>0.518809</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.434633</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.47113</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.503653</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.555916</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.5970569999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.679302</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.719116</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.301692</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.405926</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.620616</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.617941</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.532275</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.563885</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.541844</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>1.613839</v>
       </c>
     </row>
     <row r="93">
@@ -10908,7 +10908,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11576,7 +11580,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11978,7 +11986,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -16482,7 +16494,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -17428,7 +17444,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -19464,7 +19484,11 @@
           <t>Reserves 11 434,633</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -34242,19 +34266,19 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>0.27746</v>
+        <v>-0.27746</v>
       </c>
       <c r="H246" s="5" t="n">
-        <v>0.806543</v>
+        <v>-0.806543</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>0.629999</v>
+        <v>-0.629999</v>
       </c>
       <c r="J246" s="5" t="n">
-        <v>0.337789</v>
+        <v>-0.337789</v>
       </c>
       <c r="K246" s="5" t="n">
-        <v>0.988729</v>
+        <v>-0.988729</v>
       </c>
       <c r="L246" s="5" t="n">
         <v>-0.501323</v>
@@ -47313,10 +47337,10 @@
         </is>
       </c>
       <c r="J372" s="5" t="n">
-        <v>0.325213</v>
+        <v>-0.325213</v>
       </c>
       <c r="K372" s="5" t="n">
-        <v>0.954866</v>
+        <v>-0.954866</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -61511,13 +61535,13 @@
         </is>
       </c>
       <c r="H507" s="5" t="n">
-        <v>0.901388</v>
+        <v>-0.901388</v>
       </c>
       <c r="I507" s="5" t="n">
-        <v>0.679408</v>
+        <v>-0.679408</v>
       </c>
       <c r="J507" s="5" t="n">
-        <v>0.325213</v>
+        <v>-0.325213</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
@@ -64772,10 +64796,10 @@
         </is>
       </c>
       <c r="G538" s="5" t="n">
-        <v>0.404161</v>
+        <v>-0.404161</v>
       </c>
       <c r="H538" s="5" t="n">
-        <v>0.901388</v>
+        <v>-0.901388</v>
       </c>
       <c r="I538" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BEA.xlsx
+++ b/output/pdf_financials_xlsx/BEA.xlsx
@@ -1143,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.004114</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.006802</v>
       </c>
     </row>
     <row r="13">
@@ -2194,10 +2194,10 @@
         <v>-0.570635</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.503627</v>
+        <v>-0.507741</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.822031</v>
+        <v>-0.828833</v>
       </c>
     </row>
     <row r="28">
@@ -2324,10 +2324,10 @@
         <v>-0.570635</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.503627</v>
+        <v>-0.507741</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.822031</v>
+        <v>-0.828833</v>
       </c>
     </row>
     <row r="30">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018156</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.063416</v>
@@ -2612,7 +2612,7 @@
         <v>0.199281</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.409042</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.34906</v>
@@ -2624,22 +2624,22 @@
         <v>0.027349</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.019344</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009046</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.060985</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.051176</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.015058</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.441586</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.379527</v>
@@ -2651,10 +2651,10 @@
         <v>0.223242</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.529882</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.709031</v>
       </c>
     </row>
     <row r="35">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.11982</v>
+        <v>0.137976</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.619051</v>
@@ -2734,7 +2734,7 @@
         <v>0.399444</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.08620800000000001</v>
+        <v>0.49525</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.390388</v>
@@ -2746,22 +2746,22 @@
         <v>0.068567</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.009356</v>
+        <v>0.0287</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.006159</v>
+        <v>0.015205</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.003445</v>
+        <v>0.06443</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.003404</v>
+        <v>0.05458</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.002163</v>
+        <v>0.017221</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.003985</v>
+        <v>0.445571</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.6190870000000001</v>
@@ -2773,10 +2773,10 @@
         <v>0.301742</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.0376</v>
+        <v>0.567482</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.035738</v>
+        <v>0.744769</v>
       </c>
     </row>
     <row r="37">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.398226</v>
+        <v>0.38007</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.165737</v>
@@ -3466,7 +3466,7 @@
         <v>0.022191</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.415574</v>
+        <v>0.006532</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.005968</v>
@@ -3478,22 +3478,22 @@
         <v>0.00593</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.020214</v>
+        <v>0.00087</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.020664</v>
+        <v>0.011618</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.062003</v>
+        <v>0.001018</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.102691</v>
+        <v>0.051515</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.017447</v>
+        <v>0.002389</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.443519</v>
+        <v>0.001933</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.008044000000000001</v>
@@ -3505,10 +3505,10 @@
         <v>0.008640999999999999</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.534162</v>
+        <v>0.00428</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.710802</v>
+        <v>0.001771</v>
       </c>
     </row>
     <row r="49">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">

--- a/output/pdf_financials_xlsx/BEA.xlsx
+++ b/output/pdf_financials_xlsx/BEA.xlsx
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.001076</v>
       </c>
       <c r="S112" s="3" t="n">
         <v>0</v>
@@ -24358,7 +24358,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
